--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260523_204130.xlsx
@@ -5600,7 +5600,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
